--- a/list numpy torch.xlsx
+++ b/list numpy torch.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Natalya\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Natalya\Desktop\3rd year\ProcessCalculus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3A7B0BB-3934-408E-B86D-DA8514F2974E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6C11086-26CC-4079-B434-5E3ED11C58EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="166" formatCode="0.000000"/>
+    <numFmt numFmtId="164" formatCode="0.000000"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -170,28 +170,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -202,6 +183,25 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0" customBuiltin="1"/>
@@ -555,6 +555,7 @@
         <c:axId val="2052167012"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:min val="0"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -572,6 +573,7 @@
         <c:crossAx val="289538249"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
+        <c:majorUnit val="50"/>
       </c:valAx>
       <c:catAx>
         <c:axId val="289538249"/>
@@ -631,15 +633,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
+      <xdr:colOff>344805</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>52388</xdr:rowOff>
+      <xdr:rowOff>67628</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
+      <xdr:colOff>344805</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>128588</xdr:rowOff>
+      <xdr:rowOff>143828</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -662,6 +664,218 @@
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>335280</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>160020</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>243840</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="TextBox 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4A59E4DC-4C16-1CE8-82C2-2D263D44568E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7345680" y="3840480"/>
+          <a:ext cx="3596640" cy="1630680"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ru-RU" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Вывод: Список в </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Python </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ru-RU" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>-</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ru-RU" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>это массив указателей (ссылок) на объекты, хранящиеся в памяти, они могут быть разного типа,</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ru-RU" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> а </a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>NumPy</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ru-RU" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> и </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Pytorch </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ru-RU" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>хранят элементы одного типа в непрерывном блоке памяти и созданы специально для математических</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ru-RU" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> вычилений.</a:t>
+          </a:r>
+          <a:endParaRPr lang="ru-RU" sz="1100" b="0">
+            <a:latin typeface="+mn-lt"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -878,24 +1092,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7"/>
+      <c r="E1" s="13"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="9"/>
-      <c r="B2" s="8"/>
-      <c r="C2" s="9"/>
+      <c r="A2" s="11"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="11"/>
       <c r="D2" s="2" t="s">
         <v>4</v>
       </c>
@@ -904,7 +1118,7 @@
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="10">
+      <c r="A3" s="14">
         <v>100</v>
       </c>
       <c r="B3" s="1">
@@ -921,7 +1135,7 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="11"/>
+      <c r="A4" s="15"/>
       <c r="B4" s="1">
         <v>9.3996524810791002E-2</v>
       </c>
@@ -936,7 +1150,7 @@
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="12"/>
+      <c r="A5" s="16"/>
       <c r="B5" s="1">
         <v>9.7537279129028306E-2</v>
       </c>
@@ -951,7 +1165,7 @@
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="13">
+      <c r="A6" s="6">
         <v>1000</v>
       </c>
       <c r="B6" s="1">
@@ -968,7 +1182,7 @@
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="14"/>
+      <c r="A7" s="7"/>
       <c r="B7" s="1">
         <v>204.64570856094301</v>
       </c>
@@ -983,7 +1197,7 @@
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="14"/>
+      <c r="A8" s="7"/>
       <c r="B8" s="1">
         <v>209.94878578186001</v>
       </c>
@@ -998,7 +1212,7 @@
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="13">
+      <c r="A9" s="6">
         <v>10000</v>
       </c>
       <c r="B9" s="4"/>
@@ -1013,7 +1227,7 @@
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="14"/>
+      <c r="A10" s="7"/>
       <c r="B10" s="4"/>
       <c r="C10" s="1">
         <v>67.335043191909705</v>
@@ -1026,7 +1240,7 @@
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="14"/>
+      <c r="A11" s="7"/>
       <c r="B11" s="4"/>
       <c r="C11" s="1">
         <v>67.568877935409503</v>
@@ -1039,7 +1253,7 @@
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="13">
+      <c r="A12" s="6">
         <v>30000</v>
       </c>
       <c r="B12" s="4"/>
@@ -1050,7 +1264,7 @@
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="14"/>
+      <c r="A13" s="7"/>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
@@ -1059,7 +1273,7 @@
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="14"/>
+      <c r="A14" s="7"/>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
@@ -1069,33 +1283,33 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25"/>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="15" t="s">
+      <c r="A20" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B20" s="16"/>
-      <c r="C20" s="16"/>
-      <c r="D20" s="16"/>
-      <c r="E20" s="16"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="8" t="s">
+      <c r="A21" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B21" s="8" t="s">
+      <c r="B21" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="C21" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D21" s="6" t="s">
+      <c r="D21" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="E21" s="7"/>
+      <c r="E21" s="13"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="9"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="9"/>
+      <c r="A22" s="11"/>
+      <c r="B22" s="10"/>
+      <c r="C22" s="11"/>
       <c r="D22" s="2" t="s">
         <v>4</v>
       </c>
@@ -1177,6 +1391,11 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="A3:A5"/>
     <mergeCell ref="A6:A8"/>
     <mergeCell ref="A9:A11"/>
     <mergeCell ref="A20:E20"/>
@@ -1185,11 +1404,6 @@
     <mergeCell ref="C21:C22"/>
     <mergeCell ref="D21:E21"/>
     <mergeCell ref="A12:A14"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="A3:A5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/list numpy torch.xlsx
+++ b/list numpy torch.xlsx
@@ -1,232 +1,238 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Natalya\Desktop\3rd year\ProcessCalculus\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6C11086-26CC-4079-B434-5E3ED11C58EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
-  <sheets>
-    <sheet name="Лист1" sheetId="1" r:id="rId1"/>
-  </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
-</workbook>
+<s:workbook xmlns:unk3="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:unk1="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="unk1 xr xr6 xr10 xr2">
+  <s:fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <s:workbookPr/>
+  <s:bookViews>
+    <s:workbookView xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176"/>
+  </s:bookViews>
+  <s:sheets>
+    <s:sheet name="Лист1" sheetId="1" state="visible" r:id="rId1"/>
+  </s:sheets>
+  <s:calcPr calcId="191029"/>
+  <s:extLst>
+    <s:ext uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <unk3:calcFeatures>
+        <unk3:feature name="microsoft.com:RD"/>
+        <unk3:feature name="microsoft.com:Single"/>
+        <unk3:feature name="microsoft.com:FV"/>
+        <unk3:feature name="microsoft.com:CNMTM"/>
+        <unk3:feature name="microsoft.com:LET_WF"/>
+        <unk3:feature name="microsoft.com:LAMBDA_WF"/>
+        <unk3:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </unk3:calcFeatures>
+    </s:ext>
+  </s:extLst>
+</s:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="7">
-  <si>
-    <t>NxN</t>
-  </si>
-  <si>
-    <t>list</t>
-  </si>
-  <si>
-    <t>numpy</t>
-  </si>
-  <si>
-    <t>torch</t>
-  </si>
-  <si>
-    <t>CPU</t>
-  </si>
-  <si>
-    <t>GPU</t>
-  </si>
-  <si>
-    <t>Среднее:</t>
-  </si>
-</sst>
+<s:sst xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="7">
+  <s:si>
+    <s:t>NxN</s:t>
+  </s:si>
+  <s:si>
+    <s:t>list</s:t>
+  </s:si>
+  <s:si>
+    <s:t>numpy</s:t>
+  </s:si>
+  <s:si>
+    <s:t>torch</s:t>
+  </s:si>
+  <s:si>
+    <s:t>CPU</s:t>
+  </s:si>
+  <s:si>
+    <s:t>GPU</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Среднее:</s:t>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve">Ключевое различие между list python и  данными библиотеками в том, что python интерпретируемый язык, а билиотеки numpy, torch скомпилированы на более быстрых компилируемых языках (C и Fortran, c++ соответственно). </s:t>
+  </s:si>
+  <s:si>
+    <s:t>Ключевое различие между встроенным list в python и  данными библиотеками в том, что python интерпретируемый язык, а билиотеки numpy, torch скомпилированы на более быстрых компилируемых языках (C и Fortran, c++ соответственно). Torch gpu в разы быстрее, благодаря вычислениям на видеокарте, которая содержит больше алу, в отличие от cpu.</s:t>
+  </s:si>
+</s:sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.000000"/>
-  </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-  </fonts>
-  <fills count="2">
-    <fill>
-      <patternFill patternType="none"/>
-    </fill>
-    <fill>
-      <patternFill patternType="gray125"/>
-    </fill>
-  </fills>
-  <borders count="7">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-  </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-  </cellStyleXfs>
-  <cellXfs count="17">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-  </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Обычный" xfId="0" builtinId="0" customBuiltin="1"/>
-  </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+<s:styleSheet xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vyd="http://volga.yandex.com/schemas/document/model" xmlns:unk1="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <s:numFmts count="1">
+    <s:numFmt numFmtId="164" formatCode="0.000000"/>
+  </s:numFmts>
+  <s:fonts x14ac:knownFonts="1" count="2">
+    <s:font>
+      <s:name val="Arial"/>
+      <s:family val="2"/>
+      <s:color theme="1"/>
+      <s:sz val="10"/>
+    </s:font>
+    <s:font>
+      <s:name val="Arial"/>
+      <s:b val="1"/>
+      <s:sz val="10"/>
+    </s:font>
+  </s:fonts>
+  <s:fills count="2">
+    <s:fill>
+      <s:patternFill patternType="none"/>
+    </s:fill>
+    <s:fill>
+      <s:patternFill patternType="gray125"/>
+    </s:fill>
+  </s:fills>
+  <s:borders count="7">
+    <s:border>
+      <s:left/>
+      <s:right/>
+      <s:top/>
+      <s:bottom/>
+      <s:diagonal/>
+    </s:border>
+    <s:border>
+      <s:left style="thin">
+        <s:color auto="1"/>
+      </s:left>
+      <s:right style="thin">
+        <s:color auto="1"/>
+      </s:right>
+      <s:top style="thin">
+        <s:color auto="1"/>
+      </s:top>
+      <s:bottom style="thin">
+        <s:color auto="1"/>
+      </s:bottom>
+      <s:diagonal/>
+    </s:border>
+    <s:border>
+      <s:left style="thin">
+        <s:color auto="1"/>
+      </s:left>
+      <s:right style="thin">
+        <s:color auto="1"/>
+      </s:right>
+      <s:top style="thin">
+        <s:color auto="1"/>
+      </s:top>
+      <s:bottom/>
+      <s:diagonal/>
+    </s:border>
+    <s:border>
+      <s:left style="thin">
+        <s:color auto="1"/>
+      </s:left>
+      <s:right style="thin">
+        <s:color auto="1"/>
+      </s:right>
+      <s:top/>
+      <s:bottom/>
+      <s:diagonal/>
+    </s:border>
+    <s:border>
+      <s:left style="thin">
+        <s:color auto="1"/>
+      </s:left>
+      <s:right style="thin">
+        <s:color auto="1"/>
+      </s:right>
+      <s:top/>
+      <s:bottom style="thin">
+        <s:color auto="1"/>
+      </s:bottom>
+      <s:diagonal/>
+    </s:border>
+    <s:border>
+      <s:left/>
+      <s:right/>
+      <s:top/>
+      <s:bottom/>
+      <s:diagonal/>
+    </s:border>
+    <s:border>
+      <s:left/>
+      <s:right/>
+      <s:top style="thin">
+        <s:color auto="1"/>
+      </s:top>
+      <s:bottom style="thin">
+        <s:color auto="1"/>
+      </s:bottom>
+      <s:diagonal/>
+    </s:border>
+  </s:borders>
+  <s:cellStyleXfs count="1">
+    <s:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </s:cellStyleXfs>
+  <s:cellXfs count="19">
+    <s:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <s:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <s:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <s:xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <s:xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <s:xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <s:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <s:alignment horizontal="center" vertical="center" mc:Ignorable="vyd"/>
+    </s:xf>
+    <s:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <s:alignment vertical="center" mc:Ignorable="vyd"/>
+    </s:xf>
+    <s:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <s:alignment horizontal="center" mc:Ignorable="vyd"/>
+    </s:xf>
+    <s:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <s:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <s:alignment horizontal="center" vertical="center" mc:Ignorable="vyd"/>
+    </s:xf>
+    <s:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <s:alignment vertical="center" mc:Ignorable="vyd"/>
+    </s:xf>
+    <s:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <s:alignment horizontal="center" mc:Ignorable="vyd"/>
+    </s:xf>
+    <s:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <s:xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <s:alignment horizontal="center" vertical="center" mc:Ignorable="vyd"/>
+    </s:xf>
+    <s:xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <s:alignment vertical="center" mc:Ignorable="vyd"/>
+    </s:xf>
+    <s:xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <s:alignment vertical="center" mc:Ignorable="vyd"/>
+    </s:xf>
+    <s:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <s:alignment horizontal="left" mc:Ignorable="vyd"/>
+    </s:xf>
+    <s:xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <s:alignment horizontal="left" mc:Ignorable="vyd"/>
+    </s:xf>
+  </s:cellXfs>
+  <s:cellStyles count="1">
+    <s:cellStyle name="Обычный" xfId="0" builtinId="0" customBuiltin="1"/>
+  </s:cellStyles>
+  <s:dxfs count="0"/>
+  <s:tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <s:extLst>
+    <s:ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
-</styleSheet>
+    </s:ext>
+    <s:ext uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <unk1:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </s:ext>
+  </s:extLst>
+</s:styleSheet>
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+<c:chartSpace xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:vyd="http://volga.yandex.com/schemas/document/model" xmlns:unk5="http://schemas.microsoft.com/office/drawing/2014/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <c:date1904 val="0"/>
   <c:lang val="ru-RU"/>
   <c:roundedCorners val="1"/>
   <c:style val="2"/>
   <c:chart>
-    <c:title>
+    <c:title mc:Ignorable="vyd">
       <c:tx>
         <c:rich>
           <a:bodyPr lIns="0" tIns="0" rIns="0" bIns="0"/>
@@ -321,8 +327,8 @@
           </c:val>
           <c:smooth val="0"/>
           <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-3135-49D7-A87A-322CD687A63F}"/>
+            <c:ext uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <unk5:uniqueId val="{00000000-3135-49D7-A87A-322CD687A63F}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -391,8 +397,8 @@
           </c:val>
           <c:smooth val="0"/>
           <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-3135-49D7-A87A-322CD687A63F}"/>
+            <c:ext uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <unk5:uniqueId val="{00000001-3135-49D7-A87A-322CD687A63F}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -461,8 +467,8 @@
           </c:val>
           <c:smooth val="0"/>
           <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-3135-49D7-A87A-322CD687A63F}"/>
+            <c:ext uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <unk5:uniqueId val="{00000002-3135-49D7-A87A-322CD687A63F}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -534,8 +540,8 @@
           </c:val>
           <c:smooth val="0"/>
           <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-3135-49D7-A87A-322CD687A63F}"/>
+            <c:ext uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <unk5:uniqueId val="{00000003-3135-49D7-A87A-322CD687A63F}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -597,7 +603,7 @@
         <a:noFill/>
       </c:spPr>
     </c:plotArea>
-    <c:legend>
+    <c:legend mc:Ignorable="vyd">
       <c:legendPos val="b"/>
       <c:overlay val="0"/>
       <c:txPr>
@@ -629,26 +635,26 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:unk4="http://schemas.microsoft.com/office/drawing/2014/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>344805</xdr:colOff>
+      <xdr:colOff>401955</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>67628</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>344805</xdr:colOff>
+      <xdr:colOff>401955</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>143828</xdr:rowOff>
+      <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Диаграмма 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <unk4:creationId id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -660,7 +666,7 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -674,17 +680,17 @@
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>243840</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>83820</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="3" name="TextBox 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4A59E4DC-4C16-1CE8-82C2-2D263D44568E}"/>
+              <unk4:creationId id="{4A59E4DC-4C16-1CE8-82C2-2D263D44568E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -693,7 +699,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="7345680" y="3840480"/>
-          <a:ext cx="3596640" cy="1630680"/>
+          <a:ext cx="4358640" cy="1920240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -799,7 +805,7 @@
             </a:rPr>
             <a:t> а </a:t>
           </a:r>
-          <a:br>
+          <a:r>
             <a:rPr lang="en-US" sz="1100" b="0" i="0">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
@@ -809,7 +815,20 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-          </a:br>
+            <a:t>NumPy</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ru-RU" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> и </a:t>
+          </a:r>
           <a:r>
             <a:rPr lang="en-US" sz="1100" b="0" i="0">
               <a:solidFill>
@@ -820,7 +839,7 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>NumPy</a:t>
+            <a:t>Pytorch </a:t>
           </a:r>
           <a:r>
             <a:rPr lang="ru-RU" sz="1100" b="0" i="0">
@@ -832,30 +851,6 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t> и </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" b="0" i="0">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>Pytorch </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ru-RU" sz="1100" b="0" i="0">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
             <a:t>хранят элементы одного типа в непрерывном блоке памяти и созданы специально для математических</a:t>
           </a:r>
           <a:r>
@@ -869,6 +864,162 @@
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
             <a:t> вычилений.</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ru-RU" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Вычисления на </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>gpu </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ru-RU" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>быстрее, чем на </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>cpu</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ru-RU" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>, потому что видеокарты состоят из множества алу, соответственно вычисления множества однотипных арифметических действий выполняются быстро на </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>gpu</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ru-RU" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>.</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ru-RU" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Python </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ru-RU" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- интерпретируемый... </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>todo</a:t>
           </a:r>
           <a:endParaRPr lang="ru-RU" sz="1100" b="0">
             <a:latin typeface="+mn-lt"/>
@@ -1080,332 +1231,338 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E26"/>
-  <sheetFormatPr defaultColWidth="13.44140625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="10.33203125" customWidth="1"/>
-    <col min="2" max="2" width="21.21875" customWidth="1"/>
-    <col min="3" max="3" width="22.5546875" customWidth="1"/>
-    <col min="4" max="4" width="23.109375" customWidth="1"/>
-    <col min="5" max="5" width="25" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="13"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="11"/>
-      <c r="B2" s="10"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="14">
-        <v>100</v>
-      </c>
-      <c r="B3" s="1">
-        <v>8.5592269897460896E-2</v>
-      </c>
-      <c r="C3" s="1">
-        <v>4.3659210205078099E-3</v>
-      </c>
-      <c r="D3" s="1">
-        <v>1.2493133544921799E-4</v>
-      </c>
-      <c r="E3" s="1">
-        <v>7.4213999994299202E-5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="15"/>
-      <c r="B4" s="1">
-        <v>9.3996524810791002E-2</v>
-      </c>
-      <c r="C4" s="1">
-        <v>1.5916824340820299E-3</v>
-      </c>
-      <c r="D4" s="1">
-        <v>1.57833099365234E-4</v>
-      </c>
-      <c r="E4" s="1">
-        <v>1.4422700002114601E-4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="16"/>
-      <c r="B5" s="1">
-        <v>9.7537279129028306E-2</v>
-      </c>
-      <c r="C5" s="1">
-        <v>7.8363418579101493E-3</v>
-      </c>
-      <c r="D5" s="1">
-        <v>1.08718872070312E-4</v>
-      </c>
-      <c r="E5" s="1">
-        <v>4.16170000221427E-5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="6">
-        <v>1000</v>
-      </c>
-      <c r="B6" s="1">
-        <v>201.353286504745</v>
-      </c>
-      <c r="C6" s="1">
-        <v>6.3578128814697196E-2</v>
-      </c>
-      <c r="D6" s="1">
-        <v>3.9346218109130797E-2</v>
-      </c>
-      <c r="E6" s="1">
-        <v>1.2939500004449601E-4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="7"/>
-      <c r="B7" s="1">
-        <v>204.64570856094301</v>
-      </c>
-      <c r="C7" s="1">
-        <v>6.2233686447143499E-2</v>
-      </c>
-      <c r="D7" s="1">
-        <v>3.0281782150268499E-2</v>
-      </c>
-      <c r="E7" s="1">
-        <v>1.2487100002545E-4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="7"/>
-      <c r="B8" s="1">
-        <v>209.94878578186001</v>
-      </c>
-      <c r="C8" s="1">
-        <v>9.3112468719482394E-2</v>
-      </c>
-      <c r="D8" s="1">
-        <v>3.0346870422363201E-2</v>
-      </c>
-      <c r="E8" s="1">
-        <v>1.0897399999976101E-4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="6">
-        <v>10000</v>
-      </c>
-      <c r="B9" s="4"/>
-      <c r="C9" s="1">
-        <v>66.354801893234196</v>
-      </c>
-      <c r="D9" s="1">
-        <v>27.541233942999899</v>
-      </c>
-      <c r="E9" s="1">
-        <v>1.8800300000521001E-4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="7"/>
-      <c r="B10" s="4"/>
-      <c r="C10" s="1">
-        <v>67.335043191909705</v>
-      </c>
-      <c r="D10" s="1">
-        <v>32.9946868419647</v>
-      </c>
-      <c r="E10" s="1">
-        <v>1.3001899992559599E-4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="7"/>
-      <c r="B11" s="4"/>
-      <c r="C11" s="1">
-        <v>67.568877935409503</v>
-      </c>
-      <c r="D11" s="1">
-        <v>32.400273323058997</v>
-      </c>
-      <c r="E11" s="1">
-        <v>2.1128299999872901E-4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="6">
-        <v>30000</v>
-      </c>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="1">
-        <v>3.0119600000943998E-4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="7"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="1">
-        <v>1.9975300006080899E-4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="7"/>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="1">
-        <v>1.59344999929089E-4</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25"/>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="B21" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="C21" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="D21" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="E21" s="13"/>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="11"/>
-      <c r="B22" s="10"/>
-      <c r="C22" s="11"/>
-      <c r="D22" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="1">
-        <v>100</v>
-      </c>
-      <c r="B23" s="3">
-        <f>AVERAGE(B3:B5)</f>
-        <v>9.2375357945760073E-2</v>
-      </c>
-      <c r="C23" s="3">
-        <f>AVERAGE(C3:C5)</f>
-        <v>4.5979817708333296E-3</v>
-      </c>
-      <c r="D23" s="3">
-        <f>AVERAGE(D3:D5)</f>
-        <v>1.3049443562825468E-4</v>
-      </c>
-      <c r="E23" s="3">
-        <f>AVERAGE(E3:E5)</f>
-        <v>8.6686000012529301E-5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="1">
-        <v>1000</v>
-      </c>
-      <c r="B24" s="3">
-        <f>AVERAGE(B6:B8)</f>
-        <v>205.31592694918268</v>
-      </c>
-      <c r="C24" s="3">
-        <f>AVERAGE(C6:C8)</f>
-        <v>7.2974761327107701E-2</v>
-      </c>
-      <c r="D24" s="3">
-        <f>AVERAGE(D6:D8)</f>
-        <v>3.3324956893920836E-2</v>
-      </c>
-      <c r="E24" s="3">
-        <f>AVERAGE(E6:E8)</f>
-        <v>1.2108000002323567E-4</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="1">
-        <v>10000</v>
-      </c>
-      <c r="B25" s="1"/>
-      <c r="C25" s="3">
-        <f>AVERAGE(C9:C11)</f>
-        <v>67.086241006851139</v>
-      </c>
-      <c r="D25" s="3">
-        <f>AVERAGE(D9:D11)</f>
-        <v>30.978731369341201</v>
-      </c>
-      <c r="E25" s="3">
-        <f>AVERAGE(E9:E11)</f>
-        <v>1.7643499997651167E-4</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="1">
-        <v>30000</v>
-      </c>
-      <c r="B26" s="5"/>
-      <c r="C26" s="5"/>
-      <c r="D26" s="5"/>
-      <c r="E26" s="3">
-        <f>AVERAGE(E12:E14)</f>
-        <v>2.2009799999977934E-4</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="A3:A5"/>
-    <mergeCell ref="A6:A8"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="A20:E20"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="C21:C22"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="A12:A14"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
+<s:worksheet xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <s:dimension ref="A1:E26"/>
+  <s:sheetFormatPr x14ac:dyDescent="0.25" defaultColWidth="13.441" defaultRowHeight="14.25" customHeight="1"/>
+  <s:cols>
+    <s:col min="1" max="1" width="10.332" customWidth="1"/>
+    <s:col min="2" max="2" width="21.219" customWidth="1"/>
+    <s:col min="3" max="3" width="22.555" customWidth="1"/>
+    <s:col min="4" max="4" width="23.109" customWidth="1"/>
+    <s:col min="5" max="5" width="25" customWidth="1"/>
+    <s:col min="7" max="7" width="71.352" customWidth="1"/>
+  </s:cols>
+  <s:sheetData>
+    <s:row x14ac:dyDescent="0.25" r="1" spans="1:5">
+      <s:c r="A1" s="10" t="s">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="B1" s="10" t="s">
+        <s:v>1</s:v>
+      </s:c>
+      <s:c r="C1" s="10" t="s">
+        <s:v>2</s:v>
+      </s:c>
+      <s:c r="D1" s="12" t="s">
+        <s:v>3</s:v>
+      </s:c>
+      <s:c r="E1" s="13"/>
+    </s:row>
+    <s:row x14ac:dyDescent="0.25" r="2" spans="1:5">
+      <s:c r="A2" s="11"/>
+      <s:c r="B2" s="10"/>
+      <s:c r="C2" s="11"/>
+      <s:c r="D2" s="2" t="s">
+        <s:v>4</s:v>
+      </s:c>
+      <s:c r="E2" s="2" t="s">
+        <s:v>5</s:v>
+      </s:c>
+    </s:row>
+    <s:row x14ac:dyDescent="0.25" r="3" spans="1:5">
+      <s:c r="A3" s="14">
+        <s:v>100</s:v>
+      </s:c>
+      <s:c r="B3" s="1">
+        <s:v>8.5592269897460896E-2</s:v>
+      </s:c>
+      <s:c r="C3" s="1">
+        <s:v>4.3659210205078099E-3</s:v>
+      </s:c>
+      <s:c r="D3" s="1">
+        <s:v>1.2493133544921799E-4</s:v>
+      </s:c>
+      <s:c r="E3" s="1">
+        <s:v>7.4213999994299202E-5</s:v>
+      </s:c>
+    </s:row>
+    <s:row x14ac:dyDescent="0.25" r="4" spans="1:5">
+      <s:c r="A4" s="15"/>
+      <s:c r="B4" s="1">
+        <s:v>9.3996524810791002E-2</s:v>
+      </s:c>
+      <s:c r="C4" s="1">
+        <s:v>1.5916824340820299E-3</s:v>
+      </s:c>
+      <s:c r="D4" s="1">
+        <s:v>1.57833099365234E-4</s:v>
+      </s:c>
+      <s:c r="E4" s="1">
+        <s:v>1.4422700002114601E-4</s:v>
+      </s:c>
+    </s:row>
+    <s:row x14ac:dyDescent="0.25" r="5" spans="1:5">
+      <s:c r="A5" s="16"/>
+      <s:c r="B5" s="1">
+        <s:v>9.7537279129028306E-2</s:v>
+      </s:c>
+      <s:c r="C5" s="1">
+        <s:v>7.8363418579101493E-3</s:v>
+      </s:c>
+      <s:c r="D5" s="1">
+        <s:v>1.08718872070312E-4</s:v>
+      </s:c>
+      <s:c r="E5" s="1">
+        <s:v>4.16170000221427E-5</s:v>
+      </s:c>
+    </s:row>
+    <s:row x14ac:dyDescent="0.25" r="6" spans="1:5">
+      <s:c r="A6" s="6">
+        <s:v>1000</s:v>
+      </s:c>
+      <s:c r="B6" s="1">
+        <s:v>201.353286504745</s:v>
+      </s:c>
+      <s:c r="C6" s="1">
+        <s:v>6.3578128814697196E-2</s:v>
+      </s:c>
+      <s:c r="D6" s="1">
+        <s:v>3.9346218109130797E-2</s:v>
+      </s:c>
+      <s:c r="E6" s="1">
+        <s:v>1.2939500004449601E-4</s:v>
+      </s:c>
+    </s:row>
+    <s:row x14ac:dyDescent="0.25" r="7" spans="1:5">
+      <s:c r="A7" s="7"/>
+      <s:c r="B7" s="1">
+        <s:v>204.64570856094301</s:v>
+      </s:c>
+      <s:c r="C7" s="1">
+        <s:v>6.2233686447143499E-2</s:v>
+      </s:c>
+      <s:c r="D7" s="1">
+        <s:v>3.0281782150268499E-2</s:v>
+      </s:c>
+      <s:c r="E7" s="1">
+        <s:v>1.2487100002545E-4</s:v>
+      </s:c>
+    </s:row>
+    <s:row x14ac:dyDescent="0.25" r="8" spans="1:5">
+      <s:c r="A8" s="7"/>
+      <s:c r="B8" s="1">
+        <s:v>209.94878578186001</s:v>
+      </s:c>
+      <s:c r="C8" s="1">
+        <s:v>9.3112468719482394E-2</s:v>
+      </s:c>
+      <s:c r="D8" s="1">
+        <s:v>3.0346870422363201E-2</s:v>
+      </s:c>
+      <s:c r="E8" s="1">
+        <s:v>1.0897399999976101E-4</s:v>
+      </s:c>
+    </s:row>
+    <s:row x14ac:dyDescent="0.25" r="9" spans="1:5">
+      <s:c r="A9" s="6">
+        <s:v>10000</s:v>
+      </s:c>
+      <s:c r="B9" s="4"/>
+      <s:c r="C9" s="1">
+        <s:v>66.354801893234196</s:v>
+      </s:c>
+      <s:c r="D9" s="1">
+        <s:v>27.541233942999899</s:v>
+      </s:c>
+      <s:c r="E9" s="1">
+        <s:v>1.8800300000521001E-4</s:v>
+      </s:c>
+    </s:row>
+    <s:row x14ac:dyDescent="0.25" r="10" spans="1:5">
+      <s:c r="A10" s="7"/>
+      <s:c r="B10" s="4"/>
+      <s:c r="C10" s="1">
+        <s:v>67.335043191909705</s:v>
+      </s:c>
+      <s:c r="D10" s="1">
+        <s:v>32.9946868419647</s:v>
+      </s:c>
+      <s:c r="E10" s="1">
+        <s:v>1.3001899992559599E-4</s:v>
+      </s:c>
+    </s:row>
+    <s:row x14ac:dyDescent="0.25" r="11" spans="1:5">
+      <s:c r="A11" s="7"/>
+      <s:c r="B11" s="4"/>
+      <s:c r="C11" s="1">
+        <s:v>67.568877935409503</s:v>
+      </s:c>
+      <s:c r="D11" s="1">
+        <s:v>32.400273323058997</s:v>
+      </s:c>
+      <s:c r="E11" s="1">
+        <s:v>2.1128299999872901E-4</s:v>
+      </s:c>
+    </s:row>
+    <s:row x14ac:dyDescent="0.25" r="12" spans="1:5">
+      <s:c r="A12" s="6">
+        <s:v>30000</s:v>
+      </s:c>
+      <s:c r="B12" s="4"/>
+      <s:c r="C12" s="4"/>
+      <s:c r="D12" s="4"/>
+      <s:c r="E12" s="1">
+        <s:v>3.0119600000943998E-4</s:v>
+      </s:c>
+    </s:row>
+    <s:row x14ac:dyDescent="0.25" r="13" spans="1:5">
+      <s:c r="A13" s="7"/>
+      <s:c r="B13" s="4"/>
+      <s:c r="C13" s="4"/>
+      <s:c r="D13" s="4"/>
+      <s:c r="E13" s="1">
+        <s:v>1.9975300006080899E-4</s:v>
+      </s:c>
+    </s:row>
+    <s:row x14ac:dyDescent="0.25" r="14" spans="1:5">
+      <s:c r="A14" s="7"/>
+      <s:c r="B14" s="4"/>
+      <s:c r="C14" s="4"/>
+      <s:c r="D14" s="4"/>
+      <s:c r="E14" s="1">
+        <s:v>1.59344999929089E-4</s:v>
+      </s:c>
+    </s:row>
+    <s:row x14ac:dyDescent="0.25" r="19" spans="1:5"/>
+    <s:row x14ac:dyDescent="0.25" r="20" spans="1:5">
+      <s:c r="A20" s="8" t="s">
+        <s:v>6</s:v>
+      </s:c>
+      <s:c r="B20" s="9"/>
+      <s:c r="C20" s="9"/>
+      <s:c r="D20" s="9"/>
+      <s:c r="E20" s="9"/>
+    </s:row>
+    <s:row x14ac:dyDescent="0.25" r="21" spans="1:5">
+      <s:c r="A21" s="10" t="s">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="B21" s="10" t="s">
+        <s:v>1</s:v>
+      </s:c>
+      <s:c r="C21" s="10" t="s">
+        <s:v>2</s:v>
+      </s:c>
+      <s:c r="D21" s="12" t="s">
+        <s:v>3</s:v>
+      </s:c>
+      <s:c r="E21" s="13"/>
+    </s:row>
+    <s:row x14ac:dyDescent="0.25" r="22" spans="1:5">
+      <s:c r="A22" s="11"/>
+      <s:c r="B22" s="10"/>
+      <s:c r="C22" s="11"/>
+      <s:c r="D22" s="2" t="s">
+        <s:v>4</s:v>
+      </s:c>
+      <s:c r="E22" s="2" t="s">
+        <s:v>5</s:v>
+      </s:c>
+    </s:row>
+    <s:row x14ac:dyDescent="0.25" r="23" spans="1:5">
+      <s:c r="A23" s="1">
+        <s:v>100</s:v>
+      </s:c>
+      <s:c r="B23" s="3">
+        <s:f>AVERAGE(B3:B5)</s:f>
+        <s:v>9.2375357945760073E-2</s:v>
+      </s:c>
+      <s:c r="C23" s="3">
+        <s:f>AVERAGE(C3:C5)</s:f>
+        <s:v>4.5979817708333296E-3</s:v>
+      </s:c>
+      <s:c r="D23" s="3">
+        <s:f>AVERAGE(D3:D5)</s:f>
+        <s:v>1.3049443562825468E-4</s:v>
+      </s:c>
+      <s:c r="E23" s="3">
+        <s:f>AVERAGE(E3:E5)</s:f>
+        <s:v>8.6686000012529301E-5</s:v>
+      </s:c>
+    </s:row>
+    <s:row x14ac:dyDescent="0.25" r="24" spans="1:5">
+      <s:c r="A24" s="1">
+        <s:v>1000</s:v>
+      </s:c>
+      <s:c r="B24" s="3">
+        <s:f>AVERAGE(B6:B8)</s:f>
+        <s:v>205.31592694918268</s:v>
+      </s:c>
+      <s:c r="C24" s="3">
+        <s:f>AVERAGE(C6:C8)</s:f>
+        <s:v>7.2974761327107701E-2</s:v>
+      </s:c>
+      <s:c r="D24" s="3">
+        <s:f>AVERAGE(D6:D8)</s:f>
+        <s:v>3.3324956893920836E-2</s:v>
+      </s:c>
+      <s:c r="E24" s="3">
+        <s:f>AVERAGE(E6:E8)</s:f>
+        <s:v>1.2108000002323567E-4</s:v>
+      </s:c>
+    </s:row>
+    <s:row x14ac:dyDescent="0.25" r="25" spans="1:5">
+      <s:c r="A25" s="1">
+        <s:v>10000</s:v>
+      </s:c>
+      <s:c r="B25" s="1"/>
+      <s:c r="C25" s="3">
+        <s:f>AVERAGE(C9:C11)</s:f>
+        <s:v>67.086241006851139</s:v>
+      </s:c>
+      <s:c r="D25" s="3">
+        <s:f>AVERAGE(D9:D11)</s:f>
+        <s:v>30.978731369341201</s:v>
+      </s:c>
+      <s:c r="E25" s="3">
+        <s:f>AVERAGE(E9:E11)</s:f>
+        <s:v>1.7643499997651167E-4</s:v>
+      </s:c>
+    </s:row>
+    <s:row x14ac:dyDescent="0.25" r="26" spans="1:5">
+      <s:c r="A26" s="1">
+        <s:v>30000</s:v>
+      </s:c>
+      <s:c r="B26" s="5"/>
+      <s:c r="C26" s="5"/>
+      <s:c r="D26" s="5"/>
+      <s:c r="E26" s="3">
+        <s:f>AVERAGE(E12:E14)</s:f>
+        <s:v>2.2009799999977934E-4</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="27" ht="57.75" customHeight="1">
+      <s:c r="G27" s="18" t="s">
+        <s:v>8</s:v>
+      </s:c>
+    </s:row>
+  </s:sheetData>
+  <s:mergeCells count="13">
+    <s:mergeCell ref="D1:E1"/>
+    <s:mergeCell ref="B1:B2"/>
+    <s:mergeCell ref="A1:A2"/>
+    <s:mergeCell ref="C1:C2"/>
+    <s:mergeCell ref="A3:A5"/>
+    <s:mergeCell ref="A6:A8"/>
+    <s:mergeCell ref="A9:A11"/>
+    <s:mergeCell ref="A20:E20"/>
+    <s:mergeCell ref="A21:A22"/>
+    <s:mergeCell ref="B21:B22"/>
+    <s:mergeCell ref="C21:C22"/>
+    <s:mergeCell ref="D21:E21"/>
+    <s:mergeCell ref="A12:A14"/>
+  </s:mergeCells>
+  <s:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <s:drawing r:id="rId1"/>
+</s:worksheet>
 </file>